--- a/src/examples/ELV/data/ELV_ICE_flows.xlsx
+++ b/src/examples/ELV/data/ELV_ICE_flows.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="44">
   <si>
     <t xml:space="preserve">process_from</t>
   </si>
@@ -31,9 +31,15 @@
     <t xml:space="preserve">composition</t>
   </si>
   <si>
+    <t xml:space="preserve">collection_ICE</t>
+  </si>
+  <si>
     <t xml:space="preserve">dismantling_ICE</t>
   </si>
   <si>
+    <t xml:space="preserve">ELV_ICE</t>
+  </si>
+  <si>
     <t xml:space="preserve">shredding_engtrans</t>
   </si>
   <si>
@@ -67,7 +73,13 @@
     <t xml:space="preserve">smelter_cc</t>
   </si>
   <si>
-    <t xml:space="preserve">ICE_catconverter</t>
+    <t xml:space="preserve">ICE_catconv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">market_waste_oil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICE_liquids</t>
   </si>
   <si>
     <t xml:space="preserve">smelter_nonferrous</t>
@@ -82,13 +94,19 @@
     <t xml:space="preserve">ferrous</t>
   </si>
   <si>
+    <t xml:space="preserve">market_waste_glass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">glass</t>
+  </si>
+  <si>
     <t xml:space="preserve">market_waste</t>
   </si>
   <si>
-    <t xml:space="preserve">rest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">market_wasterubber</t>
+    <t xml:space="preserve">waste_shredder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">market_waste_rubber</t>
   </si>
   <si>
     <t xml:space="preserve">rubber</t>
@@ -100,6 +118,15 @@
     <t xml:space="preserve">ree</t>
   </si>
   <si>
+    <t xml:space="preserve">market_waste_slag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">slag_ree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">market_waste_plastic</t>
+  </si>
+  <si>
     <t xml:space="preserve">plastic</t>
   </si>
   <si>
@@ -118,7 +145,13 @@
     <t xml:space="preserve">market_nonferrous</t>
   </si>
   <si>
+    <t xml:space="preserve">slag_nfe</t>
+  </si>
+  <si>
     <t xml:space="preserve">market_ferrous</t>
+  </si>
+  <si>
+    <t xml:space="preserve">slag_fe</t>
   </si>
 </sst>
 </file>
@@ -128,7 +161,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -155,11 +188,6 @@
       <name val="TeX Gyre Pagella"/>
       <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="TeX Gyre Pagella"/>
-      <family val="0"/>
     </font>
   </fonts>
   <fills count="2">
@@ -217,7 +245,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -238,7 +266,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.83"/>
@@ -264,24 +292,24 @@
       <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>8</v>
@@ -292,18 +320,18 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>12</v>
@@ -314,7 +342,7 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>14</v>
@@ -330,26 +358,26 @@
       <c r="B8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="2" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C10" s="1" t="s">
@@ -361,10 +389,10 @@
         <v>6</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -372,21 +400,21 @@
         <v>6</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>20</v>
+      <c r="B13" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -394,10 +422,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -405,32 +433,32 @@
         <v>8</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>21</v>
+        <v>10</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -438,32 +466,32 @@
         <v>10</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>11</v>
+        <v>22</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>30</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -471,65 +499,98 @@
         <v>12</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>20</v>
+      <c r="B22" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>17</v>
+        <v>36</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>19</v>
+        <v>34</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B26" s="3" t="s">
         <v>20</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>21</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/src/examples/ELV/data/ELV_ICE_flows.xlsx
+++ b/src/examples/ELV/data/ELV_ICE_flows.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="45">
   <si>
     <t xml:space="preserve">process_from</t>
   </si>
@@ -74,6 +74,9 @@
   </si>
   <si>
     <t xml:space="preserve">ICE_catconv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">market_reuse_ELVcomponents</t>
   </si>
   <si>
     <t xml:space="preserve">market_waste_oil</t>
@@ -266,11 +269,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="19.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="29.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="19.33"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="4" style="1" width="11.53"/>
   </cols>
   <sheetData>
@@ -362,7 +366,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
@@ -370,18 +374,18 @@
         <v>18</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -389,10 +393,10 @@
         <v>6</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -400,10 +404,10 @@
         <v>6</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -411,21 +415,21 @@
         <v>6</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -433,10 +437,10 @@
         <v>8</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -444,21 +448,21 @@
         <v>8</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -466,21 +470,21 @@
         <v>10</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>31</v>
+        <v>23</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -488,21 +492,21 @@
         <v>16</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -510,21 +514,21 @@
         <v>12</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -532,10 +536,10 @@
         <v>14</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -543,54 +547,65 @@
         <v>14</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>21</v>
+        <v>35</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B28" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>43</v>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/src/examples/ELV/data/ELV_ICE_flows.xlsx
+++ b/src/examples/ELV/data/ELV_ICE_flows.xlsx
@@ -10,6 +10,9 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Sheet1!$A$1:$C$30</definedName>
+  </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -31,6 +34,51 @@
     <t xml:space="preserve">composition</t>
   </si>
   <si>
+    <t xml:space="preserve">shredding_engtrans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">market_waste_glass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALL_glass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shredding_elec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">market_waste_plastic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALL_plastic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shredding_batt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shredding_tyre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">market_waste_rubber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALL_rubber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">smelter_cc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">market_waste_slag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALL_slag_ree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">smelter_ferrous</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELV_ICE_fe</t>
+  </si>
+  <si>
     <t xml:space="preserve">collection_ICE</t>
   </si>
   <si>
@@ -40,121 +88,76 @@
     <t xml:space="preserve">ELV_ICE</t>
   </si>
   <si>
-    <t xml:space="preserve">shredding_engtrans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICE_engtrans</t>
+    <t xml:space="preserve">market_reuse_ELVcomponents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELV_ICE_batt</t>
   </si>
   <si>
     <t xml:space="preserve">hammermill_body</t>
   </si>
   <si>
-    <t xml:space="preserve">ICE_body</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shredding_tyre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICE_tyres</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shredding_elec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICE_elec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shredding_batt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICE_batt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">smelter_cc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICE_catconv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">market_reuse_ELVcomponents</t>
+    <t xml:space="preserve">ELV_ICE_body</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELV_ICE_catconv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELV_ICE_elec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELV_ICE_engtrans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">market_ferrous</t>
   </si>
   <si>
     <t xml:space="preserve">market_waste_oil</t>
   </si>
   <si>
-    <t xml:space="preserve">ICE_liquids</t>
+    <t xml:space="preserve">ELV_ICE_liquids</t>
   </si>
   <si>
     <t xml:space="preserve">smelter_nonferrous</t>
   </si>
   <si>
-    <t xml:space="preserve">nonferrous</t>
-  </si>
-  <si>
-    <t xml:space="preserve">smelter_ferrous</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ferrous</t>
-  </si>
-  <si>
-    <t xml:space="preserve">market_waste_glass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">glass</t>
+    <t xml:space="preserve">ELV_ICE_nfe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">market_nonferrous</t>
+  </si>
+  <si>
+    <t xml:space="preserve">market_ree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELV_ICE_ree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELV_ICE_slag_fe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELV_ICE_slag_nfe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELV_ICE_tyres</t>
   </si>
   <si>
     <t xml:space="preserve">market_waste</t>
   </si>
   <si>
-    <t xml:space="preserve">waste_shredder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">market_waste_rubber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rubber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">market_ree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">market_waste_slag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">slag_ree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">market_waste_plastic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">plastic</t>
+    <t xml:space="preserve">ELV_ICE_waste_shredder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">market_H2SO4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H2SO4</t>
   </si>
   <si>
     <t xml:space="preserve">market_lead</t>
   </si>
   <si>
     <t xml:space="preserve">Pb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">market_H2SO4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H2SO4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">market_nonferrous</t>
-  </si>
-  <si>
-    <t xml:space="preserve">slag_nfe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">market_ferrous</t>
-  </si>
-  <si>
-    <t xml:space="preserve">slag_fe</t>
   </si>
 </sst>
 </file>
@@ -261,7 +264,20 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -302,313 +318,314 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>24</v>
+        <v>13</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="2" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>22</v>
+        <v>33</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>38</v>
+      <c r="C24" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>40</v>
+      <c r="C25" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>36</v>
+        <v>10</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>24</v>
+        <v>41</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C30" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>44</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C30"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -616,5 +633,6 @@
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/src/examples/ELV/data/ELV_ICE_flows.xlsx
+++ b/src/examples/ELV/data/ELV_ICE_flows.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Sheet1!$A$1:$C$30</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Sheet1!$A$1:$C$32</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="48">
   <si>
     <t xml:space="preserve">process_from</t>
   </si>
@@ -34,130 +34,139 @@
     <t xml:space="preserve">composition</t>
   </si>
   <si>
+    <t xml:space="preserve">collection_ICE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dismantling_ICE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELV_ICE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PutOnMarket_ICE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEW_ICE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">market_reuse_ELVcomponents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shredding_batt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELV_ICE_batt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hammermill_body</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELV_ICE_body</t>
+  </si>
+  <si>
+    <t xml:space="preserve">smelter_cc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELV_ICE_catconv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shredding_elec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELV_ICE_elec</t>
+  </si>
+  <si>
     <t xml:space="preserve">shredding_engtrans</t>
   </si>
   <si>
+    <t xml:space="preserve">ELV_ICE_engtrans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">market_waste_oil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELV_ICE_liquids</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shredding_tyre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELV_ICE_tyres</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELV_ICE_parts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">smelter_ferrous</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELV_ICE_fe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">smelter_nonferrous</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELV_ICE_nfe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">market_waste</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELV_ICE_waste_shredder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">market_waste_plastic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALL_plastic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">market_H2SO4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H2SO4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">market_lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pb</t>
+  </si>
+  <si>
     <t xml:space="preserve">market_waste_glass</t>
   </si>
   <si>
     <t xml:space="preserve">ALL_glass</t>
   </si>
   <si>
-    <t xml:space="preserve">shredding_elec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">market_waste_plastic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALL_plastic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shredding_batt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shredding_tyre</t>
-  </si>
-  <si>
     <t xml:space="preserve">market_waste_rubber</t>
   </si>
   <si>
     <t xml:space="preserve">ALL_rubber</t>
   </si>
   <si>
-    <t xml:space="preserve">smelter_cc</t>
-  </si>
-  <si>
     <t xml:space="preserve">market_waste_slag</t>
   </si>
   <si>
     <t xml:space="preserve">ALL_slag_ree</t>
   </si>
   <si>
-    <t xml:space="preserve">smelter_ferrous</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ELV_ICE_fe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">collection_ICE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dismantling_ICE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ELV_ICE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">market_reuse_ELVcomponents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ELV_ICE_batt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hammermill_body</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ELV_ICE_body</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ELV_ICE_catconv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ELV_ICE_elec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ELV_ICE_engtrans</t>
+    <t xml:space="preserve">market_ree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELV_ICE_ree</t>
   </si>
   <si>
     <t xml:space="preserve">market_ferrous</t>
   </si>
   <si>
-    <t xml:space="preserve">market_waste_oil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ELV_ICE_liquids</t>
-  </si>
-  <si>
-    <t xml:space="preserve">smelter_nonferrous</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ELV_ICE_nfe</t>
+    <t xml:space="preserve">ELV_ICE_slag_fe</t>
   </si>
   <si>
     <t xml:space="preserve">market_nonferrous</t>
   </si>
   <si>
-    <t xml:space="preserve">market_ree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ELV_ICE_ree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ELV_ICE_slag_fe</t>
-  </si>
-  <si>
     <t xml:space="preserve">ELV_ICE_slag_nfe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ELV_ICE_tyres</t>
-  </si>
-  <si>
-    <t xml:space="preserve">market_waste</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ELV_ICE_waste_shredder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">market_H2SO4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H2SO4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">market_lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pb</t>
   </si>
 </sst>
 </file>
@@ -238,7 +247,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -247,11 +256,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -285,7 +298,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.83"/>
@@ -316,316 +329,338 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="2" t="s">
         <v>8</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C10" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="2" t="s">
+      <c r="C11" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="1" t="s">
+    <row r="12" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>17</v>
+        <v>30</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>17</v>
+        <v>32</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C27" s="1" t="s">
         <v>40</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C30"/>
+  <autoFilter ref="A1:C32"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/src/examples/ELV/data/ELV_ICE_flows.xlsx
+++ b/src/examples/ELV/data/ELV_ICE_flows.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="47">
   <si>
     <t xml:space="preserve">process_from</t>
   </si>
@@ -44,9 +44,6 @@
   </si>
   <si>
     <t xml:space="preserve">PutOnMarket_ICE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NEW_ICE</t>
   </si>
   <si>
     <t xml:space="preserve">market_reuse_ELVcomponents</t>
@@ -337,7 +334,7 @@
         <v>3</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -345,7 +342,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>5</v>
@@ -356,10 +353,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>9</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -367,10 +364,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -378,10 +375,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>13</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -389,10 +386,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -400,10 +397,10 @@
         <v>4</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -411,10 +408,10 @@
         <v>4</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -422,10 +419,10 @@
         <v>4</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -433,230 +430,230 @@
         <v>4</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>30</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>32</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>34</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>30</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>26</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B26" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B27" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B28" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>42</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C29" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
